--- a/docs/api-v3.5/matriz_api_notificacion_DocDigital.xlsx
+++ b/docs/api-v3.5/matriz_api_notificacion_DocDigital.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Juan Candia\Documents\1 -DOC-DIGITAL-Automatizacion API\dd-automatizacion-qa\dd-automatizacion-qa\docs\api-v3.5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBDCB9C1-9678-4A9F-967D-1A46434DE51C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31FBECDF-75B5-4972-953E-B0083412F8DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -460,10 +460,10 @@
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>215265</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>897255</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>188595</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -785,23 +785,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="42" customWidth="1"/>
-    <col min="5" max="5" width="38" customWidth="1"/>
-    <col min="6" max="6" width="48" customWidth="1"/>
-    <col min="7" max="8" width="38" customWidth="1"/>
-    <col min="9" max="9" width="10" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="36" customWidth="1"/>
-    <col min="12" max="12" width="12" customWidth="1"/>
-    <col min="13" max="13" width="16" customWidth="1"/>
-    <col min="14" max="14" width="40" customWidth="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="22.109375" defaultRowHeight="24.6" customHeight="1" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -845,7 +831,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
@@ -889,7 +875,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>28</v>
       </c>
@@ -931,7 +917,7 @@
       </c>
       <c r="N3" s="2"/>
     </row>
-    <row r="4" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>36</v>
       </c>
@@ -975,7 +961,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>45</v>
       </c>
@@ -1017,7 +1003,7 @@
       </c>
       <c r="N5" s="2"/>
     </row>
-    <row r="6" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>52</v>
       </c>
@@ -1059,7 +1045,7 @@
       </c>
       <c r="N6" s="2"/>
     </row>
-    <row r="7" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>58</v>
       </c>
@@ -1101,7 +1087,7 @@
       </c>
       <c r="N7" s="2"/>
     </row>
-    <row r="8" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>64</v>
       </c>
@@ -1143,7 +1129,7 @@
       </c>
       <c r="N8" s="2"/>
     </row>
-    <row r="9" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>70</v>
       </c>
@@ -1185,7 +1171,7 @@
       </c>
       <c r="N9" s="2"/>
     </row>
-    <row r="10" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>76</v>
       </c>
@@ -1227,7 +1213,7 @@
       </c>
       <c r="N10" s="2"/>
     </row>
-    <row r="11" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>82</v>
       </c>
@@ -1269,7 +1255,7 @@
       </c>
       <c r="N11" s="2"/>
     </row>
-    <row r="12" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>90</v>
       </c>
@@ -1313,7 +1299,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>98</v>
       </c>
@@ -1357,7 +1343,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>105</v>
       </c>

--- a/docs/api-v3.5/matriz_api_notificacion_DocDigital.xlsx
+++ b/docs/api-v3.5/matriz_api_notificacion_DocDigital.xlsx
@@ -604,7 +604,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>reports/index.html; cucumber @Notificacion_HappyPath; correo DocDigital id 89685</t>
+          <t>reports/index.html; cucumber @Notificacion_HappyPath; correo DocDigital id 89703 (JFC)</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>POST 200 OK — ids 89685, 89687, 89688; correos recibidos: 89679, 89682, 89685, 89687</t>
+          <t>POST 200 OK — correos recibidos: 89703, 89705 (QA Notificacion JFC 13:54)</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Captura bandeja correos; reports/index.html; cucumber suite completa</t>
+          <t>Captura bandeja correos 89703 y 89705; reports/index.html; cucumber suite 11/11</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>200 OK — id 89687; correo DocDigital 89687</t>
+          <t>200 OK — correo DocDigital 89705 (23-06-2026 13:54:17); materia QA Notificacion JFC</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>200 OK — id 89688 (23-06-2026 10:38:17)</t>
+          <t>200 OK — API QA acepta dependiente como principal (ver hallazgo H-01 en evidencias)</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
